--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2020_tarapaca.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2020_tarapaca.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 17:05</t>
+    <t xml:space="preserve">2026-09-09 19:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2020_tarapaca.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2020_tarapaca.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 19:34</t>
+    <t xml:space="preserve">2026-09-17 04:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2020_tarapaca.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2020_tarapaca.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 04:02</t>
+    <t xml:space="preserve">2026-09-27 02:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2020_tarapaca.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2020_tarapaca.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 02:27</t>
+    <t xml:space="preserve">2026-10-03 00:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2020_tarapaca.xlsx
+++ b/output/graficos_otras_relaciones/plot_regional_d_otrasrel_a_2020_tarapaca.xlsx
@@ -35,7 +35,7 @@
     <t xml:space="preserve">apoyo</t>
   </si>
   <si>
-    <t xml:space="preserve">Tarapaca</t>
+    <t xml:space="preserve">Tarapacá</t>
   </si>
   <si>
     <t xml:space="preserve">Campo</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-03 00:47</t>
+    <t xml:space="preserve">2026-10-05 05:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">Unidad territorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Region de Tarapaca</t>
+    <t xml:space="preserve">Region de Tarapacá</t>
   </si>
   <si>
     <t xml:space="preserve">Año</t>
